--- a/output/roomself_excel/1975.xlsx
+++ b/output/roomself_excel/1975.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3495</v>
+        <v>276990</v>
       </c>
       <c r="D2" t="n">
-        <v>667</v>
+        <v>4252</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>611</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>555</v>
       </c>
     </row>
     <row r="3">
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2087</v>
+        <v>3495</v>
       </c>
       <c r="D3" t="n">
-        <v>510</v>
+        <v>667</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>467189</v>
+        <v>2087</v>
       </c>
       <c r="D4" t="n">
-        <v>6903</v>
+        <v>510</v>
       </c>
       <c r="E4" t="n">
-        <v>1073</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>785</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>138690</v>
+        <v>302821</v>
       </c>
       <c r="D5" t="n">
-        <v>2988</v>
+        <v>4478</v>
       </c>
       <c r="E5" t="n">
-        <v>445</v>
+        <v>704</v>
       </c>
       <c r="F5" t="n">
-        <v>379</v>
+        <v>618</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90666</v>
+        <v>138690</v>
       </c>
       <c r="D6" t="n">
-        <v>2420</v>
+        <v>2988</v>
       </c>
       <c r="E6" t="n">
-        <v>313</v>
+        <v>445</v>
       </c>
       <c r="F6" t="n">
-        <v>273</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>176964</v>
+        <v>90666</v>
       </c>
       <c r="D7" t="n">
-        <v>3383</v>
+        <v>2420</v>
       </c>
       <c r="E7" t="n">
-        <v>571</v>
+        <v>309</v>
       </c>
       <c r="F7" t="n">
-        <v>488</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>61677</v>
+        <v>117300</v>
       </c>
       <c r="D8" t="n">
-        <v>1992</v>
+        <v>2740</v>
       </c>
       <c r="E8" t="n">
-        <v>281</v>
+        <v>384</v>
       </c>
       <c r="F8" t="n">
-        <v>267</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23409</v>
+        <v>61677</v>
       </c>
       <c r="D9" t="n">
-        <v>1224</v>
+        <v>1992</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27081</v>
+        <v>110400</v>
       </c>
       <c r="D10" t="n">
-        <v>1320</v>
+        <v>2800</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>489</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>276990</v>
+        <v>23828</v>
       </c>
       <c r="D11" t="n">
-        <v>4252</v>
+        <v>1236</v>
       </c>
       <c r="E11" t="n">
-        <v>611</v>
+        <v>148</v>
       </c>
       <c r="F11" t="n">
-        <v>555</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>117300</v>
+        <v>164368</v>
       </c>
       <c r="D12" t="n">
-        <v>2740</v>
+        <v>3363</v>
       </c>
       <c r="E12" t="n">
-        <v>384</v>
+        <v>18</v>
       </c>
       <c r="F12" t="n">
-        <v>379</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>110400</v>
+        <v>37835</v>
       </c>
       <c r="D13" t="n">
-        <v>2800</v>
+        <v>1584</v>
       </c>
       <c r="E13" t="n">
-        <v>489</v>
+        <v>216</v>
       </c>
       <c r="F13" t="n">
-        <v>283</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23828</v>
+        <v>27081</v>
       </c>
       <c r="D14" t="n">
-        <v>1236</v>
+        <v>1320</v>
       </c>
       <c r="E14" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37835</v>
+        <v>176964</v>
       </c>
       <c r="D15" t="n">
-        <v>1584</v>
+        <v>3383</v>
       </c>
       <c r="E15" t="n">
-        <v>216</v>
+        <v>488</v>
       </c>
       <c r="F15" t="n">
-        <v>29</v>
+        <v>442</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>23409</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1224</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/1975.xlsx
+++ b/output/roomself_excel/1975.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,77 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
         </is>
       </c>
     </row>
@@ -475,11 +540,60 @@
       <c r="D2" t="n">
         <v>4252</v>
       </c>
-      <c r="E2" t="n">
-        <v>611</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>555</v>
+        <v>85</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>138</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>125</v>
+      </c>
+      <c r="M2" t="n">
+        <v>33</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>125</v>
+      </c>
+      <c r="P2" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>468</v>
+      </c>
+      <c r="S2" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +611,21 @@
       <c r="D3" t="n">
         <v>667</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +642,21 @@
       <c r="D4" t="n">
         <v>510</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +673,45 @@
       <c r="D5" t="n">
         <v>4478</v>
       </c>
-      <c r="E5" t="n">
-        <v>704</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>618</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>63</v>
+      </c>
+      <c r="J5" t="n">
+        <v>54</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>277</v>
+      </c>
+      <c r="M5" t="n">
+        <v>17</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +728,37 @@
       <c r="D6" t="n">
         <v>2988</v>
       </c>
-      <c r="E6" t="n">
-        <v>445</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>379</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="G6" t="n">
+        <v>29</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>402</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +775,29 @@
       <c r="D7" t="n">
         <v>2420</v>
       </c>
-      <c r="E7" t="n">
-        <v>309</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>77</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="G7" t="n">
+        <v>29</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +814,37 @@
       <c r="D8" t="n">
         <v>2740</v>
       </c>
-      <c r="E8" t="n">
-        <v>384</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>379</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="G8" t="n">
+        <v>34</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>345</v>
+      </c>
+      <c r="J8" t="n">
+        <v>29</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +861,37 @@
       <c r="D9" t="n">
         <v>1992</v>
       </c>
-      <c r="E9" t="n">
-        <v>281</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>267</v>
       </c>
+      <c r="G9" t="n">
+        <v>21</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>267</v>
+      </c>
+      <c r="J9" t="n">
+        <v>29</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +908,45 @@
       <c r="D10" t="n">
         <v>2800</v>
       </c>
-      <c r="E10" t="n">
-        <v>489</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>283</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="G10" t="n">
+        <v>14</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>240</v>
+      </c>
+      <c r="J10" t="n">
+        <v>29</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>444</v>
+      </c>
+      <c r="M10" t="n">
+        <v>29</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +963,29 @@
       <c r="D11" t="n">
         <v>1236</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>148</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>29</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +1002,21 @@
       <c r="D12" t="n">
         <v>3363</v>
       </c>
-      <c r="E12" t="n">
-        <v>18</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +1033,29 @@
       <c r="D13" t="n">
         <v>1584</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>216</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>29</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1072,21 @@
       <c r="D14" t="n">
         <v>1320</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1103,45 @@
       <c r="D15" t="n">
         <v>3383</v>
       </c>
-      <c r="E15" t="n">
-        <v>488</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>442</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="G15" t="n">
+        <v>29</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>386</v>
+      </c>
+      <c r="J15" t="n">
+        <v>29</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>174</v>
+      </c>
+      <c r="M15" t="n">
+        <v>16</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1158,21 @@
       <c r="D16" t="n">
         <v>1224</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/1975.xlsx
+++ b/output/roomself_excel/1975.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:AE16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,6 +524,66 @@
           <t>ExtWallWidth_5</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -593,6 +653,54 @@
         <v>468</v>
       </c>
       <c r="S2" t="n">
+        <v>27</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>85</v>
+      </c>
+      <c r="W2" t="n">
+        <v>33</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>404</v>
+      </c>
+      <c r="AE2" t="n">
         <v>27</v>
       </c>
     </row>
@@ -626,6 +734,18 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -657,6 +777,18 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -712,6 +844,42 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>320</v>
+      </c>
+      <c r="W5" t="n">
+        <v>29</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -759,6 +927,30 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>152</v>
+      </c>
+      <c r="W6" t="n">
+        <v>29</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -798,6 +990,30 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>157</v>
+      </c>
+      <c r="W7" t="n">
+        <v>29</v>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -845,6 +1061,30 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>160</v>
+      </c>
+      <c r="W8" t="n">
+        <v>29</v>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -892,6 +1132,42 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>81</v>
+      </c>
+      <c r="W9" t="n">
+        <v>21</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>115</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -947,6 +1223,42 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>89</v>
+      </c>
+      <c r="W10" t="n">
+        <v>29</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -986,6 +1298,30 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>94</v>
+      </c>
+      <c r="W11" t="n">
+        <v>29</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1017,6 +1353,18 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1056,6 +1404,30 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>110</v>
+      </c>
+      <c r="W13" t="n">
+        <v>29</v>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1087,6 +1459,18 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1142,6 +1526,54 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AD15" t="n">
+        <v>188</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1173,6 +1605,18 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
